--- a/2023_zscore/zscore_2023_housing_tenure_burden_raw.csv.xlsx
+++ b/2023_zscore/zscore_2023_housing_tenure_burden_raw.csv.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,6 +372,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>zscore_raw</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>zscore</t>
         </is>
       </c>
@@ -391,6 +396,9 @@
       <c r="D2">
         <v>-0.2142997126438119</v>
       </c>
+      <c r="E2">
+        <v>-0.2142997126438119</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -407,6 +415,9 @@
       <c r="D3">
         <v>-0.7547043569484476</v>
       </c>
+      <c r="E3">
+        <v>-0.7547043569484476</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -423,6 +434,9 @@
       <c r="D4">
         <v>1.386443263317682</v>
       </c>
+      <c r="E4">
+        <v>1.386443263317682</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -439,6 +453,9 @@
       <c r="D5">
         <v>-0.6086833531951001</v>
       </c>
+      <c r="E5">
+        <v>-0.6086833531951001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -455,6 +472,9 @@
       <c r="D6">
         <v>-0.1070417190579073</v>
       </c>
+      <c r="E6">
+        <v>-0.1070417190579073</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -471,6 +491,9 @@
       <c r="D7">
         <v>-0.3635719358032359</v>
       </c>
+      <c r="E7">
+        <v>-0.3635719358032359</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -487,6 +510,9 @@
       <c r="D8">
         <v>-0.462755938996544</v>
       </c>
+      <c r="E8">
+        <v>-0.462755938996544</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -503,6 +529,9 @@
       <c r="D9">
         <v>-0.7016569205091254</v>
       </c>
+      <c r="E9">
+        <v>-0.7016569205091254</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -529,6 +558,9 @@
       <c r="D11">
         <v>0.1754354308360503</v>
       </c>
+      <c r="E11">
+        <v>0.1754354308360503</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -545,6 +577,9 @@
       <c r="D12">
         <v>1.107549312977968</v>
       </c>
+      <c r="E12">
+        <v>1.107549312977968</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -561,6 +596,9 @@
       <c r="D13">
         <v>0.9601734024233687</v>
       </c>
+      <c r="E13">
+        <v>0.9601734024233687</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -577,6 +615,9 @@
       <c r="D14">
         <v>-0.4160282524998574</v>
       </c>
+      <c r="E14">
+        <v>-0.4160282524998574</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -593,6 +634,9 @@
       <c r="D15">
         <v>-0.7386889940565869</v>
       </c>
+      <c r="E15">
+        <v>-0.7386889940565869</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -609,6 +653,9 @@
       <c r="D16">
         <v>-0.2917437247304011</v>
       </c>
+      <c r="E16">
+        <v>-0.2917437247304011</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -625,6 +672,9 @@
       <c r="D17">
         <v>-0.6427749819513086</v>
       </c>
+      <c r="E17">
+        <v>-0.6427749819513086</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -641,6 +691,9 @@
       <c r="D18">
         <v>0.9065129218530625</v>
       </c>
+      <c r="E18">
+        <v>0.9065129218530625</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -657,6 +710,9 @@
       <c r="D19">
         <v>-1.382662154470017</v>
       </c>
+      <c r="E19">
+        <v>-1.382662154470017</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -673,6 +729,9 @@
       <c r="D20">
         <v>0.6612420982552244</v>
       </c>
+      <c r="E20">
+        <v>0.6612420982552244</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -689,6 +748,9 @@
       <c r="D21">
         <v>-1.040357315922946</v>
       </c>
+      <c r="E21">
+        <v>-1.040357315922946</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -705,6 +767,9 @@
       <c r="D22">
         <v>-0.5683615395170014</v>
       </c>
+      <c r="E22">
+        <v>-0.5683615395170014</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -721,6 +786,9 @@
       <c r="D23">
         <v>-2.02033216822244</v>
       </c>
+      <c r="E23">
+        <v>-2.02033216822244</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -737,6 +805,9 @@
       <c r="D24">
         <v>0.478334987075601</v>
       </c>
+      <c r="E24">
+        <v>0.478334987075601</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -753,6 +824,9 @@
       <c r="D25">
         <v>-1.903059325681111</v>
       </c>
+      <c r="E25">
+        <v>-1.903059325681111</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -769,6 +843,9 @@
       <c r="D26">
         <v>0.5591799351323872</v>
       </c>
+      <c r="E26">
+        <v>0.5591799351323872</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -785,6 +862,9 @@
       <c r="D27">
         <v>-0.004638716819814739</v>
       </c>
+      <c r="E27">
+        <v>-0.004638716819814739</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -801,6 +881,9 @@
       <c r="D28">
         <v>-0.8372595180786128</v>
       </c>
+      <c r="E28">
+        <v>-0.8372595180786128</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -817,6 +900,9 @@
       <c r="D29">
         <v>-1.196896671362916</v>
       </c>
+      <c r="E29">
+        <v>-1.196896671362916</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -833,6 +919,9 @@
       <c r="D30">
         <v>0.2354107383421499</v>
       </c>
+      <c r="E30">
+        <v>0.2354107383421499</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -849,6 +938,9 @@
       <c r="D31">
         <v>-0.2549371711323445</v>
       </c>
+      <c r="E31">
+        <v>-0.2549371711323445</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -865,6 +957,9 @@
       <c r="D32">
         <v>-0.1728224940393184</v>
       </c>
+      <c r="E32">
+        <v>-0.1728224940393184</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -881,6 +976,9 @@
       <c r="D33">
         <v>-1.44756447215989</v>
       </c>
+      <c r="E33">
+        <v>-1.44756447215989</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -897,6 +995,9 @@
       <c r="D34">
         <v>0.4194815792960508</v>
       </c>
+      <c r="E34">
+        <v>0.4194815792960508</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -913,6 +1014,9 @@
       <c r="D35">
         <v>-0.3811846810899234</v>
       </c>
+      <c r="E35">
+        <v>-0.3811846810899234</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -929,6 +1033,9 @@
       <c r="D36">
         <v>0.4746649048979584</v>
       </c>
+      <c r="E36">
+        <v>0.4746649048979584</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -945,6 +1052,9 @@
       <c r="D37">
         <v>1.142783579248342</v>
       </c>
+      <c r="E37">
+        <v>1.142783579248342</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -961,6 +1071,9 @@
       <c r="D38">
         <v>-0.5968993779608843</v>
       </c>
+      <c r="E38">
+        <v>-0.5968993779608843</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -977,6 +1090,9 @@
       <c r="D39">
         <v>-0.5633252322256702</v>
       </c>
+      <c r="E39">
+        <v>-0.5633252322256702</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -993,6 +1109,9 @@
       <c r="D40">
         <v>-1.365642538451709</v>
       </c>
+      <c r="E40">
+        <v>-1.365642538451709</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1009,6 +1128,9 @@
       <c r="D41">
         <v>0.731761777439914</v>
       </c>
+      <c r="E41">
+        <v>0.731761777439914</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1025,6 +1147,9 @@
       <c r="D42">
         <v>0.9172746270659919</v>
       </c>
+      <c r="E42">
+        <v>0.9172746270659919</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1041,6 +1166,9 @@
       <c r="D43">
         <v>0.6584941256982245</v>
       </c>
+      <c r="E43">
+        <v>0.6584941256982245</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1057,6 +1185,9 @@
       <c r="D44">
         <v>-0.567699244053737</v>
       </c>
+      <c r="E44">
+        <v>-0.567699244053737</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1073,6 +1204,9 @@
       <c r="D45">
         <v>0.7599665754781812</v>
       </c>
+      <c r="E45">
+        <v>0.7599665754781812</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1089,6 +1223,9 @@
       <c r="D46">
         <v>-0.4861342344062926</v>
       </c>
+      <c r="E46">
+        <v>-0.4861342344062926</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1105,6 +1242,9 @@
       <c r="D47">
         <v>-0.6785124199654562</v>
       </c>
+      <c r="E47">
+        <v>-0.6785124199654562</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1121,6 +1261,9 @@
       <c r="D48">
         <v>-1.27528744880497</v>
       </c>
+      <c r="E48">
+        <v>-1.27528744880497</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1137,6 +1280,9 @@
       <c r="D49">
         <v>-1.066854926495318</v>
       </c>
+      <c r="E49">
+        <v>-1.066854926495318</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1153,6 +1299,9 @@
       <c r="D50">
         <v>1.16613291506128</v>
       </c>
+      <c r="E50">
+        <v>1.16613291506128</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1169,6 +1318,9 @@
       <c r="D51">
         <v>1.786710427716943</v>
       </c>
+      <c r="E51">
+        <v>1.786710427716943</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1185,6 +1337,9 @@
       <c r="D52">
         <v>0.08193954643685486</v>
       </c>
+      <c r="E52">
+        <v>0.08193954643685486</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1201,6 +1356,9 @@
       <c r="D53">
         <v>0.9919762585372114</v>
       </c>
+      <c r="E53">
+        <v>0.9919762585372114</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1217,6 +1375,9 @@
       <c r="D54">
         <v>-0.2359235754786915</v>
       </c>
+      <c r="E54">
+        <v>-0.2359235754786915</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1233,6 +1394,9 @@
       <c r="D55">
         <v>-1.442678695166157</v>
       </c>
+      <c r="E55">
+        <v>-1.442678695166157</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1249,6 +1413,9 @@
       <c r="D56">
         <v>-1.167684873451875</v>
       </c>
+      <c r="E56">
+        <v>-1.167684873451875</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1265,6 +1432,9 @@
       <c r="D57">
         <v>-2.182995540433295</v>
       </c>
+      <c r="E57">
+        <v>-2.182995540433295</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1281,6 +1451,9 @@
       <c r="D58">
         <v>0.3738538496528167</v>
       </c>
+      <c r="E58">
+        <v>0.3738538496528167</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1297,6 +1470,9 @@
       <c r="D59">
         <v>0.4279696871389712</v>
       </c>
+      <c r="E59">
+        <v>0.4279696871389712</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1313,6 +1489,9 @@
       <c r="D60">
         <v>-1.83373553054785</v>
       </c>
+      <c r="E60">
+        <v>-1.83373553054785</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1329,6 +1508,9 @@
       <c r="D61">
         <v>0.1926090654070828</v>
       </c>
+      <c r="E61">
+        <v>0.1926090654070828</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1345,6 +1527,9 @@
       <c r="D62">
         <v>-0.9000747540035556</v>
       </c>
+      <c r="E62">
+        <v>-0.9000747540035556</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1361,6 +1546,9 @@
       <c r="D63">
         <v>-1.261490239288436</v>
       </c>
+      <c r="E63">
+        <v>-1.261490239288436</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1377,6 +1565,9 @@
       <c r="D64">
         <v>-0.6057500152072037</v>
       </c>
+      <c r="E64">
+        <v>-0.6057500152072037</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1393,6 +1584,9 @@
       <c r="D65">
         <v>-0.8181435701094035</v>
       </c>
+      <c r="E65">
+        <v>-0.8181435701094035</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1409,6 +1603,9 @@
       <c r="D66">
         <v>0.3982682804863215</v>
       </c>
+      <c r="E66">
+        <v>0.3982682804863215</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1425,6 +1622,9 @@
       <c r="D67">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E67">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1441,6 +1641,9 @@
       <c r="D68">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E68">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1457,6 +1660,9 @@
       <c r="D69">
         <v>-1.299801947764965</v>
       </c>
+      <c r="E69">
+        <v>-1.299801947764965</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -1473,6 +1679,9 @@
       <c r="D70">
         <v>-1.22114452660156</v>
       </c>
+      <c r="E70">
+        <v>-1.22114452660156</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1489,6 +1698,9 @@
       <c r="D71">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E71">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -1505,6 +1717,9 @@
       <c r="D72">
         <v>-0.9265364451793499</v>
       </c>
+      <c r="E72">
+        <v>-0.9265364451793499</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -1521,6 +1736,9 @@
       <c r="D73">
         <v>-0.9014553639779449</v>
       </c>
+      <c r="E73">
+        <v>-0.9014553639779449</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -1537,6 +1755,9 @@
       <c r="D74">
         <v>0.1506183076562107</v>
       </c>
+      <c r="E74">
+        <v>0.1506183076562107</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -1553,6 +1774,9 @@
       <c r="D75">
         <v>0.9754714137547679</v>
       </c>
+      <c r="E75">
+        <v>0.9754714137547679</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -1569,6 +1793,9 @@
       <c r="D76">
         <v>1.120113296776724</v>
       </c>
+      <c r="E76">
+        <v>1.120113296776724</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1585,6 +1812,9 @@
       <c r="D77">
         <v>0.1727720761577022</v>
       </c>
+      <c r="E77">
+        <v>0.1727720761577022</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -1601,6 +1831,9 @@
       <c r="D78">
         <v>-0.6768486666519302</v>
       </c>
+      <c r="E78">
+        <v>-0.6768486666519302</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1617,6 +1850,9 @@
       <c r="D79">
         <v>-2.00053688979561</v>
       </c>
+      <c r="E79">
+        <v>-2.00053688979561</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -1633,6 +1869,9 @@
       <c r="D80">
         <v>-0.09688809622500989</v>
       </c>
+      <c r="E80">
+        <v>-0.09688809622500989</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -1649,6 +1888,9 @@
       <c r="D81">
         <v>0.49561602883128</v>
       </c>
+      <c r="E81">
+        <v>0.49561602883128</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -1665,6 +1907,9 @@
       <c r="D82">
         <v>1.419380683192063</v>
       </c>
+      <c r="E82">
+        <v>1.419380683192063</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -1681,6 +1926,9 @@
       <c r="D83">
         <v>0.8064929123243447</v>
       </c>
+      <c r="E83">
+        <v>0.8064929123243447</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -1697,6 +1945,9 @@
       <c r="D84">
         <v>0.9018318640959521</v>
       </c>
+      <c r="E84">
+        <v>0.9018318640959521</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -1713,6 +1964,9 @@
       <c r="D85">
         <v>-0.4399991724787855</v>
       </c>
+      <c r="E85">
+        <v>-0.4399991724787855</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -1729,6 +1983,9 @@
       <c r="D86">
         <v>-0.1006285950449788</v>
       </c>
+      <c r="E86">
+        <v>-0.1006285950449788</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -1745,6 +2002,9 @@
       <c r="D87">
         <v>-0.298610830570097</v>
       </c>
+      <c r="E87">
+        <v>-0.298610830570097</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -1761,6 +2021,9 @@
       <c r="D88">
         <v>1.238664494644202</v>
       </c>
+      <c r="E88">
+        <v>1.238664494644202</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -1777,6 +2040,9 @@
       <c r="D89">
         <v>0.4389393228471405</v>
       </c>
+      <c r="E89">
+        <v>0.4389393228471405</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -1793,6 +2059,9 @@
       <c r="D90">
         <v>-0.03987377826301437</v>
       </c>
+      <c r="E90">
+        <v>-0.03987377826301437</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -1809,6 +2078,9 @@
       <c r="D91">
         <v>1.854776309476452</v>
       </c>
+      <c r="E91">
+        <v>1.854776309476452</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -1825,6 +2097,9 @@
       <c r="D92">
         <v>-0.8613809091657826</v>
       </c>
+      <c r="E92">
+        <v>-0.8613809091657826</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -1841,6 +2116,9 @@
       <c r="D93">
         <v>0.5290013064446353</v>
       </c>
+      <c r="E93">
+        <v>0.5290013064446353</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -1857,6 +2135,9 @@
       <c r="D94">
         <v>-0.2629694283555006</v>
       </c>
+      <c r="E94">
+        <v>-0.2629694283555006</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -1873,6 +2154,9 @@
       <c r="D95">
         <v>-1.222189190250457</v>
       </c>
+      <c r="E95">
+        <v>-1.222189190250457</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -1889,6 +2173,9 @@
       <c r="D96">
         <v>0.7118636993110978</v>
       </c>
+      <c r="E96">
+        <v>0.7118636993110978</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -1905,6 +2192,9 @@
       <c r="D97">
         <v>2.029896001436262</v>
       </c>
+      <c r="E97">
+        <v>2.029896001436262</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -1921,6 +2211,9 @@
       <c r="D98">
         <v>0.9548177601478176</v>
       </c>
+      <c r="E98">
+        <v>0.9548177601478176</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -1937,6 +2230,9 @@
       <c r="D99">
         <v>1.112856099996961</v>
       </c>
+      <c r="E99">
+        <v>1.112856099996961</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -1953,6 +2249,9 @@
       <c r="D100">
         <v>-0.9700734163214114</v>
       </c>
+      <c r="E100">
+        <v>-0.9700734163214114</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -1969,6 +2268,9 @@
       <c r="D101">
         <v>-0.3318435242427253</v>
       </c>
+      <c r="E101">
+        <v>-0.3318435242427253</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -1985,6 +2287,9 @@
       <c r="D102">
         <v>-0.4042860028850058</v>
       </c>
+      <c r="E102">
+        <v>-0.4042860028850058</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -2001,6 +2306,9 @@
       <c r="D103">
         <v>-0.7655145444581347</v>
       </c>
+      <c r="E103">
+        <v>-0.7655145444581347</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -2017,6 +2325,9 @@
       <c r="D104">
         <v>1.140721973620352</v>
       </c>
+      <c r="E104">
+        <v>1.140721973620352</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -2033,6 +2344,9 @@
       <c r="D105">
         <v>1.494765345827927</v>
       </c>
+      <c r="E105">
+        <v>1.494765345827927</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -2049,6 +2363,9 @@
       <c r="D106">
         <v>0.2120657148851312</v>
       </c>
+      <c r="E106">
+        <v>0.2120657148851312</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -2065,6 +2382,9 @@
       <c r="D107">
         <v>1.231075275353739</v>
       </c>
+      <c r="E107">
+        <v>1.231075275353739</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -2081,6 +2401,9 @@
       <c r="D108">
         <v>0.2766792468674631</v>
       </c>
+      <c r="E108">
+        <v>0.2766792468674631</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -2097,6 +2420,9 @@
       <c r="D109">
         <v>0.2525261261795464</v>
       </c>
+      <c r="E109">
+        <v>0.2525261261795464</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -2113,6 +2439,9 @@
       <c r="D110">
         <v>0.3782426943281548</v>
       </c>
+      <c r="E110">
+        <v>0.3782426943281548</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -2129,6 +2458,9 @@
       <c r="D111">
         <v>-0.9302107436993009</v>
       </c>
+      <c r="E111">
+        <v>-0.9302107436993009</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -2145,6 +2477,9 @@
       <c r="D112">
         <v>-1.06254523510892</v>
       </c>
+      <c r="E112">
+        <v>-1.06254523510892</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -2161,6 +2496,9 @@
       <c r="D113">
         <v>-1.166519240656186</v>
       </c>
+      <c r="E113">
+        <v>-1.166519240656186</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -2177,6 +2515,9 @@
       <c r="D114">
         <v>0.02806629602809936</v>
       </c>
+      <c r="E114">
+        <v>0.02806629602809936</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -2193,6 +2534,9 @@
       <c r="D115">
         <v>-0.2815943571432219</v>
       </c>
+      <c r="E115">
+        <v>-0.2815943571432219</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -2209,6 +2553,9 @@
       <c r="D116">
         <v>-0.6527700673199462</v>
       </c>
+      <c r="E116">
+        <v>-0.6527700673199462</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -2225,6 +2572,9 @@
       <c r="D117">
         <v>-0.1704269140814147</v>
       </c>
+      <c r="E117">
+        <v>-0.1704269140814147</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -2241,6 +2591,9 @@
       <c r="D118">
         <v>1.25477812800525</v>
       </c>
+      <c r="E118">
+        <v>1.25477812800525</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -2257,6 +2610,9 @@
       <c r="D119">
         <v>1.348874977148113</v>
       </c>
+      <c r="E119">
+        <v>1.348874977148113</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -2273,6 +2629,9 @@
       <c r="D120">
         <v>0.557297168400314</v>
       </c>
+      <c r="E120">
+        <v>0.557297168400314</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -2289,6 +2648,9 @@
       <c r="D121">
         <v>-0.08803341353893644</v>
       </c>
+      <c r="E121">
+        <v>-0.08803341353893644</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -2305,6 +2667,9 @@
       <c r="D122">
         <v>-0.4155989909907286</v>
       </c>
+      <c r="E122">
+        <v>-0.4155989909907286</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -2321,6 +2686,9 @@
       <c r="D123">
         <v>0.2413321348801883</v>
       </c>
+      <c r="E123">
+        <v>0.2413321348801883</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -2337,6 +2705,9 @@
       <c r="D124">
         <v>-0.3981050940023798</v>
       </c>
+      <c r="E124">
+        <v>-0.3981050940023798</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -2353,6 +2724,9 @@
       <c r="D125">
         <v>0.09084341228127739</v>
       </c>
+      <c r="E125">
+        <v>0.09084341228127739</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -2369,6 +2743,9 @@
       <c r="D126">
         <v>-1.06830831942797</v>
       </c>
+      <c r="E126">
+        <v>-1.06830831942797</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -2385,6 +2762,9 @@
       <c r="D127">
         <v>-0.5516402840636121</v>
       </c>
+      <c r="E127">
+        <v>-0.5516402840636121</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -2401,6 +2781,9 @@
       <c r="D128">
         <v>0.2586586465015873</v>
       </c>
+      <c r="E128">
+        <v>0.2586586465015873</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -2417,6 +2800,9 @@
       <c r="D129">
         <v>0.07857931261954096</v>
       </c>
+      <c r="E129">
+        <v>0.07857931261954096</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -2433,6 +2819,9 @@
       <c r="D130">
         <v>-0.1994819078676163</v>
       </c>
+      <c r="E130">
+        <v>-0.1994819078676163</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -2449,6 +2838,9 @@
       <c r="D131">
         <v>0.3197384560155969</v>
       </c>
+      <c r="E131">
+        <v>0.3197384560155969</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -2465,6 +2857,9 @@
       <c r="D132">
         <v>-0.7825791442800828</v>
       </c>
+      <c r="E132">
+        <v>-0.7825791442800828</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -2481,6 +2876,9 @@
       <c r="D133">
         <v>-0.7851854511237495</v>
       </c>
+      <c r="E133">
+        <v>-0.7851854511237495</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -2497,6 +2895,9 @@
       <c r="D134">
         <v>0.6480065673854479</v>
       </c>
+      <c r="E134">
+        <v>0.6480065673854479</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -2513,6 +2914,9 @@
       <c r="D135">
         <v>-0.2039156857253472</v>
       </c>
+      <c r="E135">
+        <v>-0.2039156857253472</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -2529,6 +2933,9 @@
       <c r="D136">
         <v>0.4944310083175018</v>
       </c>
+      <c r="E136">
+        <v>0.4944310083175018</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -2545,6 +2952,9 @@
       <c r="D137">
         <v>2.028374733325417</v>
       </c>
+      <c r="E137">
+        <v>2.028374733325417</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -2561,6 +2971,9 @@
       <c r="D138">
         <v>0.9482743746256723</v>
       </c>
+      <c r="E138">
+        <v>0.9482743746256723</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -2577,6 +2990,9 @@
       <c r="D139">
         <v>0.7577546231919224</v>
       </c>
+      <c r="E139">
+        <v>0.7577546231919224</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -2593,6 +3009,9 @@
       <c r="D140">
         <v>1.092490591533751</v>
       </c>
+      <c r="E140">
+        <v>1.092490591533751</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -2609,6 +3028,9 @@
       <c r="D141">
         <v>0.01499504177366501</v>
       </c>
+      <c r="E141">
+        <v>0.01499504177366501</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -2625,6 +3047,9 @@
       <c r="D142">
         <v>0.1158684910685168</v>
       </c>
+      <c r="E142">
+        <v>0.1158684910685168</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -2641,6 +3066,9 @@
       <c r="D143">
         <v>0.3029792464202817</v>
       </c>
+      <c r="E143">
+        <v>0.3029792464202817</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -2657,6 +3085,9 @@
       <c r="D144">
         <v>-0.970731737457632</v>
       </c>
+      <c r="E144">
+        <v>-0.970731737457632</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -2673,6 +3104,9 @@
       <c r="D145">
         <v>-0.6299954690470757</v>
       </c>
+      <c r="E145">
+        <v>-0.6299954690470757</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -2689,6 +3123,9 @@
       <c r="D146">
         <v>0.9594169079408659</v>
       </c>
+      <c r="E146">
+        <v>0.9594169079408659</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -2705,6 +3142,9 @@
       <c r="D147">
         <v>-0.1245535804222295</v>
       </c>
+      <c r="E147">
+        <v>-0.1245535804222295</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -2721,6 +3161,9 @@
       <c r="D148">
         <v>0.1802173236657095</v>
       </c>
+      <c r="E148">
+        <v>0.1802173236657095</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -2737,6 +3180,9 @@
       <c r="D149">
         <v>0.402483719476314</v>
       </c>
+      <c r="E149">
+        <v>0.402483719476314</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -2753,6 +3199,9 @@
       <c r="D150">
         <v>0.3935285586663761</v>
       </c>
+      <c r="E150">
+        <v>0.3935285586663761</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -2769,6 +3218,9 @@
       <c r="D151">
         <v>0.1175752629817515</v>
       </c>
+      <c r="E151">
+        <v>0.1175752629817515</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -2785,6 +3237,9 @@
       <c r="D152">
         <v>0.6051392378443816</v>
       </c>
+      <c r="E152">
+        <v>0.6051392378443816</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -2801,6 +3256,9 @@
       <c r="D153">
         <v>0.0236523299052026</v>
       </c>
+      <c r="E153">
+        <v>0.0236523299052026</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -2817,6 +3275,9 @@
       <c r="D154">
         <v>0.2495139427451711</v>
       </c>
+      <c r="E154">
+        <v>0.2495139427451711</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -2833,6 +3294,9 @@
       <c r="D155">
         <v>1.007836432575406</v>
       </c>
+      <c r="E155">
+        <v>1.007836432575406</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -2849,6 +3313,9 @@
       <c r="D156">
         <v>0.03206679734372118</v>
       </c>
+      <c r="E156">
+        <v>0.03206679734372118</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -2865,6 +3332,9 @@
       <c r="D157">
         <v>0.2342981774677594</v>
       </c>
+      <c r="E157">
+        <v>0.2342981774677594</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -2881,6 +3351,9 @@
       <c r="D158">
         <v>-0.2328540866601431</v>
       </c>
+      <c r="E158">
+        <v>-0.2328540866601431</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -2897,6 +3370,9 @@
       <c r="D159">
         <v>-0.8153914651302587</v>
       </c>
+      <c r="E159">
+        <v>-0.8153914651302587</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -2913,6 +3389,9 @@
       <c r="D160">
         <v>-0.3057796854445767</v>
       </c>
+      <c r="E160">
+        <v>-0.3057796854445767</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -2929,6 +3408,9 @@
       <c r="D161">
         <v>-0.783238802901259</v>
       </c>
+      <c r="E161">
+        <v>-0.783238802901259</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -2945,6 +3427,9 @@
       <c r="D162">
         <v>-0.8266944488583724</v>
       </c>
+      <c r="E162">
+        <v>-0.8266944488583724</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -2961,6 +3446,9 @@
       <c r="D163">
         <v>0.4663811620303857</v>
       </c>
+      <c r="E163">
+        <v>0.4663811620303857</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -2977,6 +3465,9 @@
       <c r="D164">
         <v>0.1036676224980599</v>
       </c>
+      <c r="E164">
+        <v>0.1036676224980599</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -2993,6 +3484,9 @@
       <c r="D165">
         <v>-0.8862085061047503</v>
       </c>
+      <c r="E165">
+        <v>-0.8862085061047503</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -3009,6 +3503,9 @@
       <c r="D166">
         <v>1.482444946120125</v>
       </c>
+      <c r="E166">
+        <v>1.482444946120125</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -3025,6 +3522,9 @@
       <c r="D167">
         <v>0.4917319128160745</v>
       </c>
+      <c r="E167">
+        <v>0.4917319128160745</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -3041,6 +3541,9 @@
       <c r="D168">
         <v>-0.2331968157331436</v>
       </c>
+      <c r="E168">
+        <v>-0.2331968157331436</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -3057,6 +3560,9 @@
       <c r="D169">
         <v>-0.6479649492714372</v>
       </c>
+      <c r="E169">
+        <v>-0.6479649492714372</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -3073,6 +3579,9 @@
       <c r="D170">
         <v>0.4942603584335727</v>
       </c>
+      <c r="E170">
+        <v>0.4942603584335727</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -3089,6 +3598,9 @@
       <c r="D171">
         <v>0.6956843273991939</v>
       </c>
+      <c r="E171">
+        <v>0.6956843273991939</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -3105,6 +3617,9 @@
       <c r="D172">
         <v>0.2907246631725386</v>
       </c>
+      <c r="E172">
+        <v>0.2907246631725386</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -3121,6 +3636,9 @@
       <c r="D173">
         <v>-1.262703434240909</v>
       </c>
+      <c r="E173">
+        <v>-1.262703434240909</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -3137,6 +3655,9 @@
       <c r="D174">
         <v>0.05466468703573744</v>
       </c>
+      <c r="E174">
+        <v>0.05466468703573744</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -3153,6 +3674,9 @@
       <c r="D175">
         <v>-0.3179539215947428</v>
       </c>
+      <c r="E175">
+        <v>-0.3179539215947428</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -3169,6 +3693,9 @@
       <c r="D176">
         <v>0.4776008692825861</v>
       </c>
+      <c r="E176">
+        <v>0.4776008692825861</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -3185,6 +3712,9 @@
       <c r="D177">
         <v>0.3314459770067817</v>
       </c>
+      <c r="E177">
+        <v>0.3314459770067817</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -3201,6 +3731,9 @@
       <c r="D178">
         <v>-0.785799976132324</v>
       </c>
+      <c r="E178">
+        <v>-0.785799976132324</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -3217,6 +3750,9 @@
       <c r="D179">
         <v>0.01246491883381384</v>
       </c>
+      <c r="E179">
+        <v>0.01246491883381384</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -3233,6 +3769,9 @@
       <c r="D180">
         <v>0.7706167161157202</v>
       </c>
+      <c r="E180">
+        <v>0.7706167161157202</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -3249,6 +3788,9 @@
       <c r="D181">
         <v>1.833540075338339</v>
       </c>
+      <c r="E181">
+        <v>1.833540075338339</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -3265,6 +3807,9 @@
       <c r="D182">
         <v>0.3105565936845893</v>
       </c>
+      <c r="E182">
+        <v>0.3105565936845893</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -3281,6 +3826,9 @@
       <c r="D183">
         <v>0.8116401713118849</v>
       </c>
+      <c r="E183">
+        <v>0.8116401713118849</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -3297,6 +3845,9 @@
       <c r="D184">
         <v>0.09303866970567133</v>
       </c>
+      <c r="E184">
+        <v>0.09303866970567133</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -3313,6 +3864,9 @@
       <c r="D185">
         <v>0.9580983676030619</v>
       </c>
+      <c r="E185">
+        <v>0.9580983676030619</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -3329,6 +3883,9 @@
       <c r="D186">
         <v>0.8040581577175937</v>
       </c>
+      <c r="E186">
+        <v>0.8040581577175937</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -3345,6 +3902,9 @@
       <c r="D187">
         <v>0.7880341336166961</v>
       </c>
+      <c r="E187">
+        <v>0.7880341336166961</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -3361,6 +3921,9 @@
       <c r="D188">
         <v>0.7284990314786006</v>
       </c>
+      <c r="E188">
+        <v>0.7284990314786006</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -3377,6 +3940,9 @@
       <c r="D189">
         <v>0.6196442898615567</v>
       </c>
+      <c r="E189">
+        <v>0.6196442898615567</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -3393,6 +3959,9 @@
       <c r="D190">
         <v>0.9886549153599345</v>
       </c>
+      <c r="E190">
+        <v>0.9886549153599345</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -3409,6 +3978,9 @@
       <c r="D191">
         <v>0.04070680270414285</v>
       </c>
+      <c r="E191">
+        <v>0.04070680270414285</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -3425,6 +3997,9 @@
       <c r="D192">
         <v>-0.271008186506265</v>
       </c>
+      <c r="E192">
+        <v>-0.271008186506265</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -3441,6 +4016,9 @@
       <c r="D193">
         <v>0.2808359458736918</v>
       </c>
+      <c r="E193">
+        <v>0.2808359458736918</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -3457,6 +4035,9 @@
       <c r="D194">
         <v>1.524171348184778</v>
       </c>
+      <c r="E194">
+        <v>1.524171348184778</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -3473,6 +4054,9 @@
       <c r="D195">
         <v>-0.2894592339993902</v>
       </c>
+      <c r="E195">
+        <v>-0.2894592339993902</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -3489,6 +4073,9 @@
       <c r="D196">
         <v>2.443135874305667</v>
       </c>
+      <c r="E196">
+        <v>2.443135874305667</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -3505,6 +4092,9 @@
       <c r="D197">
         <v>1.181500193721642</v>
       </c>
+      <c r="E197">
+        <v>1.181500193721642</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -3521,6 +4111,9 @@
       <c r="D198">
         <v>-0.0802376872756549</v>
       </c>
+      <c r="E198">
+        <v>-0.0802376872756549</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -3537,6 +4130,9 @@
       <c r="D199">
         <v>0.6012879880799196</v>
       </c>
+      <c r="E199">
+        <v>0.6012879880799196</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -3553,6 +4149,9 @@
       <c r="D200">
         <v>0.2485586555531429</v>
       </c>
+      <c r="E200">
+        <v>0.2485586555531429</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -3569,6 +4168,9 @@
       <c r="D201">
         <v>0.05115471545569959</v>
       </c>
+      <c r="E201">
+        <v>0.05115471545569959</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -3585,6 +4187,9 @@
       <c r="D202">
         <v>2.555255077315691</v>
       </c>
+      <c r="E202">
+        <v>2.555255077315691</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -3601,6 +4206,9 @@
       <c r="D203">
         <v>0.7475610830525732</v>
       </c>
+      <c r="E203">
+        <v>0.7475610830525732</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -3617,6 +4225,9 @@
       <c r="D204">
         <v>1.007823998124102</v>
       </c>
+      <c r="E204">
+        <v>1.007823998124102</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -3633,6 +4244,9 @@
       <c r="D205">
         <v>0.7959333004269977</v>
       </c>
+      <c r="E205">
+        <v>0.7959333004269977</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -3649,6 +4263,9 @@
       <c r="D206">
         <v>0.7649486751662504</v>
       </c>
+      <c r="E206">
+        <v>0.7649486751662504</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -3665,6 +4282,9 @@
       <c r="D207">
         <v>1.062060839724472</v>
       </c>
+      <c r="E207">
+        <v>1.062060839724472</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -3681,6 +4301,9 @@
       <c r="D208">
         <v>0.6100682022306209</v>
       </c>
+      <c r="E208">
+        <v>0.6100682022306209</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -3697,6 +4320,9 @@
       <c r="D209">
         <v>-0.01592983420420193</v>
       </c>
+      <c r="E209">
+        <v>-0.01592983420420193</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -3713,6 +4339,9 @@
       <c r="D210">
         <v>-1.164543628328347</v>
       </c>
+      <c r="E210">
+        <v>-1.164543628328347</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -3729,6 +4358,9 @@
       <c r="D211">
         <v>-1.071436151267088</v>
       </c>
+      <c r="E211">
+        <v>-1.071436151267088</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -3745,6 +4377,9 @@
       <c r="D212">
         <v>-0.4515026600775269</v>
       </c>
+      <c r="E212">
+        <v>-0.4515026600775269</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -3761,6 +4396,9 @@
       <c r="D213">
         <v>1.521664152693937</v>
       </c>
+      <c r="E213">
+        <v>1.521664152693937</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -3777,6 +4415,9 @@
       <c r="D214">
         <v>-0.5587759528865053</v>
       </c>
+      <c r="E214">
+        <v>-0.5587759528865053</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -3793,6 +4434,9 @@
       <c r="D215">
         <v>0.4144870782775893</v>
       </c>
+      <c r="E215">
+        <v>0.4144870782775893</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -3809,6 +4453,9 @@
       <c r="D216">
         <v>2.13758992964684</v>
       </c>
+      <c r="E216">
+        <v>2.13758992964684</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -3825,6 +4472,9 @@
       <c r="D217">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E217">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -3841,6 +4491,9 @@
       <c r="D218">
         <v>0.9022479224209662</v>
       </c>
+      <c r="E218">
+        <v>0.9022479224209662</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -3857,6 +4510,9 @@
       <c r="D219">
         <v>0.1671609396145773</v>
       </c>
+      <c r="E219">
+        <v>0.1671609396145773</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -3873,6 +4529,9 @@
       <c r="D220">
         <v>1.092182766097448</v>
       </c>
+      <c r="E220">
+        <v>1.092182766097448</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -3889,6 +4548,9 @@
       <c r="D221">
         <v>0.5929807841140856</v>
       </c>
+      <c r="E221">
+        <v>0.5929807841140856</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -3905,6 +4567,9 @@
       <c r="D222">
         <v>0.5083167731013759</v>
       </c>
+      <c r="E222">
+        <v>0.5083167731013759</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -3921,6 +4586,9 @@
       <c r="D223">
         <v>-0.3167797353543497</v>
       </c>
+      <c r="E223">
+        <v>-0.3167797353543497</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -3937,6 +4605,9 @@
       <c r="D224">
         <v>-0.0923882284487524</v>
       </c>
+      <c r="E224">
+        <v>-0.0923882284487524</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -3953,6 +4624,9 @@
       <c r="D225">
         <v>1.032121012362928</v>
       </c>
+      <c r="E225">
+        <v>1.032121012362928</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -3969,6 +4643,9 @@
       <c r="D226">
         <v>2.119714873370241</v>
       </c>
+      <c r="E226">
+        <v>2.119714873370241</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -3985,6 +4662,9 @@
       <c r="D227">
         <v>-0.9081258642974676</v>
       </c>
+      <c r="E227">
+        <v>-0.9081258642974676</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -4001,6 +4681,9 @@
       <c r="D228">
         <v>0.7795745721526954</v>
       </c>
+      <c r="E228">
+        <v>0.7795745721526954</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -4017,6 +4700,9 @@
       <c r="D229">
         <v>-0.9014553639779449</v>
       </c>
+      <c r="E229">
+        <v>-0.9014553639779449</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -4033,6 +4719,9 @@
       <c r="D230">
         <v>-1.982211887270274</v>
       </c>
+      <c r="E230">
+        <v>-1.982211887270274</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -4049,6 +4738,9 @@
       <c r="D231">
         <v>0.1598923888615093</v>
       </c>
+      <c r="E231">
+        <v>0.1598923888615093</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -4065,6 +4757,9 @@
       <c r="D232">
         <v>1.243771163152978</v>
       </c>
+      <c r="E232">
+        <v>1.243771163152978</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -4081,6 +4776,9 @@
       <c r="D233">
         <v>2.885415742155858</v>
       </c>
+      <c r="E233">
+        <v>2.885415742155858</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -4097,6 +4795,9 @@
       <c r="D234">
         <v>2.584814923017347</v>
       </c>
+      <c r="E234">
+        <v>2.584814923017347</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -4113,6 +4814,9 @@
       <c r="D235">
         <v>0.3154889330902253</v>
       </c>
+      <c r="E235">
+        <v>0.3154889330902253</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -4129,6 +4833,9 @@
       <c r="D236">
         <v>0.3670516030390026</v>
       </c>
+      <c r="E236">
+        <v>0.3670516030390026</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -4145,6 +4852,9 @@
       <c r="D237">
         <v>-0.4499959023526553</v>
       </c>
+      <c r="E237">
+        <v>-0.4499959023526553</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -4161,6 +4871,9 @@
       <c r="D238">
         <v>1.037922293244207</v>
       </c>
+      <c r="E238">
+        <v>1.037922293244207</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -4177,6 +4890,9 @@
       <c r="D239">
         <v>1.288265974072179</v>
       </c>
+      <c r="E239">
+        <v>1.288265974072179</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -4193,6 +4909,9 @@
       <c r="D240">
         <v>0.7110677573120096</v>
       </c>
+      <c r="E240">
+        <v>0.7110677573120096</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -4209,6 +4928,9 @@
       <c r="D241">
         <v>0.2196755029310788</v>
       </c>
+      <c r="E241">
+        <v>0.2196755029310788</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -4225,6 +4947,9 @@
       <c r="D242">
         <v>1.280274550868018</v>
       </c>
+      <c r="E242">
+        <v>1.280274550868018</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -4241,6 +4966,9 @@
       <c r="D243">
         <v>-0.1578676417095905</v>
       </c>
+      <c r="E243">
+        <v>-0.1578676417095905</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -4257,6 +4985,9 @@
       <c r="D244">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E244">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -4273,6 +5004,9 @@
       <c r="D245">
         <v>-0.9509110170511377</v>
       </c>
+      <c r="E245">
+        <v>-0.9509110170511377</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -4289,6 +5023,9 @@
       <c r="D246">
         <v>0.4218892055540663</v>
       </c>
+      <c r="E246">
+        <v>0.4218892055540663</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -4305,6 +5042,9 @@
       <c r="D247">
         <v>-0.8544283367253105</v>
       </c>
+      <c r="E247">
+        <v>-0.8544283367253105</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -4321,6 +5061,9 @@
       <c r="D248">
         <v>0.4944310083175018</v>
       </c>
+      <c r="E248">
+        <v>0.4944310083175018</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -4337,6 +5080,9 @@
       <c r="D249">
         <v>0.7011193739174811</v>
       </c>
+      <c r="E249">
+        <v>0.7011193739174811</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -4353,6 +5099,9 @@
       <c r="D250">
         <v>0.4563071928989839</v>
       </c>
+      <c r="E250">
+        <v>0.4563071928989839</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -4369,6 +5118,9 @@
       <c r="D251">
         <v>-0.413767673950626</v>
       </c>
+      <c r="E251">
+        <v>-0.413767673950626</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -4385,6 +5137,9 @@
       <c r="D252">
         <v>-2.026738183400215</v>
       </c>
+      <c r="E252">
+        <v>-2.026738183400215</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -4401,6 +5156,9 @@
       <c r="D253">
         <v>0.8626013744822592</v>
       </c>
+      <c r="E253">
+        <v>0.8626013744822592</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -4417,6 +5175,9 @@
       <c r="D254">
         <v>1.198318319049032</v>
       </c>
+      <c r="E254">
+        <v>1.198318319049032</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -4433,6 +5194,9 @@
       <c r="D255">
         <v>-0.2824568490521051</v>
       </c>
+      <c r="E255">
+        <v>-0.2824568490521051</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -4449,6 +5213,9 @@
       <c r="D256">
         <v>-0.809360768941536</v>
       </c>
+      <c r="E256">
+        <v>-0.809360768941536</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -4465,6 +5232,9 @@
       <c r="D257">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E257">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -4481,6 +5251,9 @@
       <c r="D258">
         <v>-1.864294073598397</v>
       </c>
+      <c r="E258">
+        <v>-1.864294073598397</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -4497,6 +5270,9 @@
       <c r="D259">
         <v>0.7852874240816788</v>
       </c>
+      <c r="E259">
+        <v>0.7852874240816788</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -4513,6 +5289,9 @@
       <c r="D260">
         <v>-0.2818051225314687</v>
       </c>
+      <c r="E260">
+        <v>-0.2818051225314687</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -4529,6 +5308,9 @@
       <c r="D261">
         <v>-1.0313114837681</v>
       </c>
+      <c r="E261">
+        <v>-1.0313114837681</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -4545,6 +5327,9 @@
       <c r="D262">
         <v>-0.87912289441505</v>
       </c>
+      <c r="E262">
+        <v>-0.87912289441505</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -4561,6 +5346,9 @@
       <c r="D263">
         <v>-1.034698607860409</v>
       </c>
+      <c r="E263">
+        <v>-1.034698607860409</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -4577,6 +5365,9 @@
       <c r="D264">
         <v>-1.254670820116488</v>
       </c>
+      <c r="E264">
+        <v>-1.254670820116488</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -4593,6 +5384,9 @@
       <c r="D265">
         <v>1.080472573458078</v>
       </c>
+      <c r="E265">
+        <v>1.080472573458078</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266">
@@ -4609,6 +5403,9 @@
       <c r="D266">
         <v>-1.075555682735228</v>
       </c>
+      <c r="E266">
+        <v>-1.075555682735228</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267">
@@ -4625,6 +5422,9 @@
       <c r="D267">
         <v>-1.293072245894619</v>
       </c>
+      <c r="E267">
+        <v>-1.293072245894619</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268">
@@ -4641,6 +5441,9 @@
       <c r="D268">
         <v>-0.1625802691257442</v>
       </c>
+      <c r="E268">
+        <v>-0.1625802691257442</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269">
@@ -4657,6 +5460,9 @@
       <c r="D269">
         <v>-2.657131048076293</v>
       </c>
+      <c r="E269">
+        <v>-2.657131048076293</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270">
@@ -4673,6 +5479,9 @@
       <c r="D270">
         <v>-1.368986198023552</v>
       </c>
+      <c r="E270">
+        <v>-1.368986198023552</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271">
@@ -4689,6 +5498,9 @@
       <c r="D271">
         <v>0.2670687417649323</v>
       </c>
+      <c r="E271">
+        <v>0.2670687417649323</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272">
@@ -4705,6 +5517,9 @@
       <c r="D272">
         <v>-1.322028952682727</v>
       </c>
+      <c r="E272">
+        <v>-1.322028952682727</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273">
@@ -4721,6 +5536,9 @@
       <c r="D273">
         <v>0.6797687717171886</v>
       </c>
+      <c r="E273">
+        <v>0.6797687717171886</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274">
@@ -4737,6 +5555,9 @@
       <c r="D274">
         <v>-0.5001580647554653</v>
       </c>
+      <c r="E274">
+        <v>-0.5001580647554653</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275">
@@ -4753,6 +5574,9 @@
       <c r="D275">
         <v>0.6055033415892694</v>
       </c>
+      <c r="E275">
+        <v>0.6055033415892694</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276">
@@ -4769,6 +5593,9 @@
       <c r="D276">
         <v>-0.07252732265215828</v>
       </c>
+      <c r="E276">
+        <v>-0.07252732265215828</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277">
@@ -4785,6 +5612,9 @@
       <c r="D277">
         <v>-0.0296301098880116</v>
       </c>
+      <c r="E277">
+        <v>-0.0296301098880116</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278">
@@ -4801,6 +5631,9 @@
       <c r="D278">
         <v>0.07462197748731193</v>
       </c>
+      <c r="E278">
+        <v>0.07462197748731193</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279">
@@ -4817,6 +5650,9 @@
       <c r="D279">
         <v>0.06503956017574765</v>
       </c>
+      <c r="E279">
+        <v>0.06503956017574765</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280">
@@ -4843,6 +5679,9 @@
       <c r="D281">
         <v>0.6583767542806959</v>
       </c>
+      <c r="E281">
+        <v>0.6583767542806959</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282">
@@ -4859,6 +5698,9 @@
       <c r="D282">
         <v>-0.03803193641233687</v>
       </c>
+      <c r="E282">
+        <v>-0.03803193641233687</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283">
@@ -4875,6 +5717,9 @@
       <c r="D283">
         <v>-1.097255629398311</v>
       </c>
+      <c r="E283">
+        <v>-1.097255629398311</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284">
@@ -4891,6 +5736,9 @@
       <c r="D284">
         <v>-0.3679847479480615</v>
       </c>
+      <c r="E284">
+        <v>-0.3679847479480615</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285">
@@ -4905,6 +5753,9 @@
         <v>35.12422360248447</v>
       </c>
       <c r="D285">
+        <v>-0.6309379881627912</v>
+      </c>
+      <c r="E285">
         <v>-0.6309379881627912</v>
       </c>
     </row>
